--- a/Project_CNN/ResNet/Results/Unified Training Metrics - ResNet BS32 500EPS.xlsx
+++ b/Project_CNN/ResNet/Results/Unified Training Metrics - ResNet BS32 500EPS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\Main\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\ResNet\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5F4899-0F32-46BD-BE61-05E26B39EF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7680869-62C9-49E1-9E4E-F1A684B88B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -152,7 +152,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -12589,7 +12588,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -26765,15 +26763,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>6349</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>13607</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -26801,16 +26799,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>56</xdr:col>
+      <xdr:colOff>503465</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>145596</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>295276</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>295277</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -26825,8 +26823,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="33250909" y="2771775"/>
-          <a:ext cx="2849708" cy="2905126"/>
+          <a:off x="43202679" y="3003096"/>
+          <a:ext cx="4690384" cy="4303940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -26857,7 +26855,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" b="1" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26868,7 +26866,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26876,7 +26874,7 @@
             <a:t>ResNet 50: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26888,7 +26886,7 @@
             <a:t>0,871853</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26896,7 +26894,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600" baseline="0">
+          <a:endParaRPr lang="pt-BR" sz="2400" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -26921,7 +26919,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26933,7 +26931,7 @@
             <a:t>ResNet 34: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26945,7 +26943,7 @@
             <a:t>0,919127</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26953,7 +26951,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600">
+          <a:endParaRPr lang="pt-BR" sz="2400">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -26978,7 +26976,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -26990,7 +26988,7 @@
             <a:t>ResNet 18: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27002,7 +27000,7 @@
             <a:t>0,90038</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27030,7 +27028,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27042,7 +27040,7 @@
             <a:t>ResNet 10: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27054,7 +27052,7 @@
             <a:t>0,862163</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27062,7 +27060,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600" baseline="0">
+          <a:endParaRPr lang="pt-BR" sz="2400" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27074,7 +27072,7 @@
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="pt-BR" sz="1600" b="0" baseline="0">
+          <a:endParaRPr lang="pt-BR" sz="2400" b="0" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27087,7 +27085,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" b="1" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27098,7 +27096,7 @@
             </a:rPr>
             <a:t>Max Validation accuracy</a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600" b="1">
+          <a:endParaRPr lang="pt-BR" sz="2400" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27107,7 +27105,7 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27119,7 +27117,7 @@
             <a:t>ResNet 50: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27131,7 +27129,7 @@
             <a:t>0,875</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27143,7 +27141,7 @@
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27155,7 +27153,7 @@
             <a:t>ResNet 34: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27167,7 +27165,7 @@
             <a:t>0,900799</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27179,7 +27177,7 @@
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27191,7 +27189,7 @@
             <a:t>ResNet 18: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27203,7 +27201,7 @@
             <a:t>0,890625</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27215,7 +27213,7 @@
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2400" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27227,7 +27225,7 @@
             <a:t>ResNet 10: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27239,7 +27237,7 @@
             <a:t>0,881177</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2400">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27280,16 +27278,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>603916</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>15096</xdr:colOff>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>4321</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>612320</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27316,16 +27314,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>450272</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>86591</xdr:rowOff>
+      <xdr:col>56</xdr:col>
+      <xdr:colOff>136073</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>72984</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>269298</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>82263</xdr:rowOff>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>82511</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -27340,8 +27338,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="33224931" y="11516591"/>
-          <a:ext cx="2849708" cy="2853172"/>
+          <a:off x="42835287" y="11312484"/>
+          <a:ext cx="4232688" cy="3900302"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -27372,7 +27370,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" b="1" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27383,7 +27381,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27391,7 +27389,7 @@
             <a:t>ResNet 50: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27403,7 +27401,7 @@
             <a:t>1,41863</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27411,7 +27409,7 @@
             </a:rPr>
             <a:t>  </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600" baseline="0">
+          <a:endParaRPr lang="pt-BR" sz="2000" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27436,7 +27434,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27448,7 +27446,7 @@
             <a:t>ResNet 34: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27460,7 +27458,7 @@
             <a:t>0,701864</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27468,7 +27466,7 @@
             </a:rPr>
             <a:t>  </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600">
+          <a:endParaRPr lang="pt-BR" sz="2000">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27493,7 +27491,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27505,7 +27503,7 @@
             <a:t>ResNet 18: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27517,7 +27515,7 @@
             <a:t>0,51979</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27545,7 +27543,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27557,7 +27555,7 @@
             <a:t>ResNet 10: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27569,7 +27567,7 @@
             <a:t>0,494418</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27577,7 +27575,7 @@
             </a:rPr>
             <a:t>  </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600" baseline="0">
+          <a:endParaRPr lang="pt-BR" sz="2000" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27589,7 +27587,7 @@
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="pt-BR" sz="1600" b="0" baseline="0">
+          <a:endParaRPr lang="pt-BR" sz="2000" b="0" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27602,7 +27600,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" b="1" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27613,7 +27611,7 @@
             </a:rPr>
             <a:t>Min Validation Loss</a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1600" b="1">
+          <a:endParaRPr lang="pt-BR" sz="2000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -27622,7 +27620,7 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27634,7 +27632,7 @@
             <a:t>ResNet 50: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27646,7 +27644,7 @@
             <a:t>1,436752</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27658,7 +27656,7 @@
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27670,7 +27668,7 @@
             <a:t>ResNet 34: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27682,7 +27680,7 @@
             <a:t>0,787056</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27694,7 +27692,7 @@
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27706,7 +27704,7 @@
             <a:t>ResNet 18: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27718,7 +27716,7 @@
             <a:t>0,577009</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27730,7 +27728,7 @@
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" baseline="0">
+            <a:rPr lang="pt-BR" sz="2000" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27742,7 +27740,7 @@
             <a:t>ResNet 10: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -27754,7 +27752,7 @@
             <a:t>0,470442</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600">
+            <a:rPr lang="pt-BR" sz="2000">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -28106,29 +28104,28 @@
       <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -30081,10 +30078,10 @@
       <c r="T40">
         <v>0.67142820358276001</v>
       </c>
-      <c r="V40" s="5" t="s">
+      <c r="V40" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="W40" s="5" t="s">
+      <c r="W40" s="4" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Project_CNN/ResNet/Results/Unified Training Metrics - ResNet BS32 500EPS.xlsx
+++ b/Project_CNN/ResNet/Results/Unified Training Metrics - ResNet BS32 500EPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\ResNet\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5618B1B-F012-4D39-A8E0-4CF949A1CC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0CCC5B-8EED-4B30-ABC9-44D754A8E328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,7 +222,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="pt-BR" baseline="0"/>
-              <a:t>Accuracy Curves</a:t>
+              <a:t>Curvas de Acurácia no treino</a:t>
             </a:r>
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
@@ -2024,14 +2024,16 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Accuracy</a:t>
+                  <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Acurácia (%)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> (%)</a:t>
-                </a:r>
-                <a:endParaRPr lang="pt-BR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2218,14 +2220,16 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Validation</a:t>
+              <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Curvas de Acurácia na validação</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="pt-BR" baseline="0"/>
-              <a:t> Accuracy Curves</a:t>
-            </a:r>
-            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -4035,7 +4039,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pt-BR"/>
-                  <a:t>Accuracy</a:t>
+                  <a:t>Acurácia</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="pt-BR" baseline="0"/>
@@ -4229,7 +4233,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="pt-BR"/>
-              <a:t>Loss Curves</a:t>
+              <a:t>Curvas de Perda no treino</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5908,7 +5912,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pt-BR"/>
-                  <a:t>Epochs</a:t>
+                  <a:t>Épocas</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -6026,7 +6030,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pt-BR"/>
-                  <a:t>Loss</a:t>
+                  <a:t>Perda</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -6212,12 +6216,15 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Validation</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="pt-BR" baseline="0"/>
-              <a:t> Loss Curves</a:t>
+              <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Curvas de Perda na validação</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -7895,9 +7902,17 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Epochs</a:t>
+                  <a:rPr lang="pt-BR" sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Épocas</a:t>
                 </a:r>
+                <a:endParaRPr lang="pt-BR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -8013,8 +8028,15 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Loss</a:t>
+                  <a:rPr lang="pt-BR" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Perda</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -10395,15 +10417,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>792062</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>2847</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>492473</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>159991</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>458968</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>164937</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10430,16 +10452,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>490931</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>463716</xdr:colOff>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>1421</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>161412</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>824105</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>166357</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10469,15 +10491,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>791440</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>165086</xdr:rowOff>
+      <xdr:colOff>2226</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>165087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>490931</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>457088</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>138523</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10504,16 +10526,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>490931</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>463716</xdr:colOff>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>162636</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>26294</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>130899</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>830035</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
